--- a/output/Spinning_working.xlsx
+++ b/output/Spinning_working.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikhitha\OneDrive\Desktop\Manning_AUM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://welspungroup-my.sharepoint.com/personal/sahith_thadimudupula_welspun_com/Documents/Desktop/spinning_git/Spinning/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27A5A94-B1FD-49F2-9F70-8465DE6A863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A27A5A94-B1FD-49F2-9F70-8465DE6A863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56933B42-5AE6-4DC6-97FF-74D6146AA73F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spinning" sheetId="1" r:id="rId1"/>
@@ -957,36 +957,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="31">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1354,6 +1324,36 @@
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1368,29 +1368,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}" name="Table1" displayName="Table1" ref="A1:T117" totalsRowShown="0" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}" name="Table1" displayName="Table1" ref="A1:T117" totalsRowShown="0" dataDxfId="20">
   <autoFilter ref="A1:T117" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{85A1F019-9DB7-48AC-AF2B-F0C9FBE637DA}" name="Location" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{545588E2-5E30-4A62-AB93-1DBC57F6BCF8}" name="Business" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{44C3C497-13A6-40FF-AABF-EC930E13E039}" name="Section" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{ED8F8366-2CFD-45B1-B1C2-AA92F55B23F6}" name="Sr_No" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{3C440E90-56BF-4BC4-ACD0-A73E98969A14}" name="Dept_Machine_Name" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{EADE3DD8-7C1C-4874-8032-AD8F2F81A125}" name="Designation" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{292F7B89-A9FA-4B1D-8581-9D4596E679FF}" name="Machine_Count" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{090D3B71-C4CF-432F-B817-104F30316591}" name="Workload" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{9EDB9484-B177-478C-9BA3-4C1AE3030F95}" name="Formulas" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{3A1186F6-9294-4AEC-A543-A07372ADEF4D}" name="BE_Scientific_Manpower" dataDxfId="20"/>
-    <tableColumn id="20" xr3:uid="{071CCBE0-65D5-467E-AFCC-8949549E1BB6}" name="Operator_Type" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{F5544431-B0F5-4C79-B5EB-61614939F4B5}" name="Contractors" dataDxfId="18"/>
-    <tableColumn id="19" xr3:uid="{15BE4AF0-E211-4DE0-800A-0EDB9C705B37}" name="Company_Associate" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{47E45710-4EB9-4699-B8AD-09AC38DE8C54}" name="BE_Final_Manpower" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{38203A5B-662C-436E-A752-C238B552EF03}" name="General_Shift" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{3D149A8F-3122-4C7E-B50D-02B6DF1691E0}" name="Shift_A" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{0AFA7034-EEDB-4D14-A601-C01016D3A7D5}" name="Shift_B" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{64D43A66-597F-4C18-84E0-E76FCB0F95CC}" name="Shift_C" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{554EDC51-4B6D-44FF-BB2C-DA6797B32110}" name="Reliever" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{FF4E975E-F83C-4D1D-8950-072C414D6E58}" name="Remarks" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{85A1F019-9DB7-48AC-AF2B-F0C9FBE637DA}" name="Location" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{545588E2-5E30-4A62-AB93-1DBC57F6BCF8}" name="Business" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{44C3C497-13A6-40FF-AABF-EC930E13E039}" name="Section" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{ED8F8366-2CFD-45B1-B1C2-AA92F55B23F6}" name="Sr_No" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{3C440E90-56BF-4BC4-ACD0-A73E98969A14}" name="Dept_Machine_Name" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{EADE3DD8-7C1C-4874-8032-AD8F2F81A125}" name="Designation" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{292F7B89-A9FA-4B1D-8581-9D4596E679FF}" name="Machine_Count" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{090D3B71-C4CF-432F-B817-104F30316591}" name="Workload" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{9EDB9484-B177-478C-9BA3-4C1AE3030F95}" name="Formulas" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{3A1186F6-9294-4AEC-A543-A07372ADEF4D}" name="BE_Scientific_Manpower" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{071CCBE0-65D5-467E-AFCC-8949549E1BB6}" name="Operator_Type" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{F5544431-B0F5-4C79-B5EB-61614939F4B5}" name="Contractors" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{15BE4AF0-E211-4DE0-800A-0EDB9C705B37}" name="Company_Associate" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{47E45710-4EB9-4699-B8AD-09AC38DE8C54}" name="BE_Final_Manpower" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{38203A5B-662C-436E-A752-C238B552EF03}" name="General_Shift" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{3D149A8F-3122-4C7E-B50D-02B6DF1691E0}" name="Shift_A" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{0AFA7034-EEDB-4D14-A601-C01016D3A7D5}" name="Shift_B" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{64D43A66-597F-4C18-84E0-E76FCB0F95CC}" name="Shift_C" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{554EDC51-4B6D-44FF-BB2C-DA6797B32110}" name="Reliever" dataDxfId="1"/>
+    <tableColumn id="18" xr3:uid="{FF4E975E-F83C-4D1D-8950-072C414D6E58}" name="Remarks" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1421,18 +1421,18 @@
       <calculatedColumnFormula>L2/I2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{7C882653-B2FB-4460-945F-BEC827034FAE}" name="formula_No. of TFO Required/ shift "/>
-    <tableColumn id="14" xr3:uid="{74DD064C-08DB-4132-A242-1290AD15CDB8}" name="No. of TFO Required/ shift " dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{74DD064C-08DB-4132-A242-1290AD15CDB8}" name="No. of TFO Required/ shift " dataDxfId="30" totalsRowDxfId="29"/>
     <tableColumn id="15" xr3:uid="{65F3003E-C476-4D6D-BE1A-6488E17CDB9D}" name="mpm"/>
-    <tableColumn id="16" xr3:uid="{6E9D763E-DE2C-4A86-B1EA-5287AC19467B}" name="Eff" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{4C4EE216-BFC8-45EA-BA92-DA7C3E734438}" name="Formula_kgs/drum/day " dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{6E9D763E-DE2C-4A86-B1EA-5287AC19467B}" name="Eff" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="17" xr3:uid="{4C4EE216-BFC8-45EA-BA92-DA7C3E734438}" name="Formula_kgs/drum/day " dataDxfId="26" totalsRowDxfId="25"/>
     <tableColumn id="18" xr3:uid="{00170897-62B8-4C84-AE04-5EAE44ABC362}" name="kgs/drum/day ">
       <calculatedColumnFormula>Q2*R2*8*60*1.09/(C2*840*2.202)*3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{2DD7DB04-94B4-4773-9E4C-D99D0E582A8C}" name="formula_No. of Drums"/>
-    <tableColumn id="20" xr3:uid="{B964DFB3-EA94-419A-8A86-F1F5917ADCA3}" name="No. of Drums " dataDxfId="3" totalsRowDxfId="2">
+    <tableColumn id="20" xr3:uid="{B964DFB3-EA94-419A-8A86-F1F5917ADCA3}" name="No. of Drums " dataDxfId="24" totalsRowDxfId="23">
       <calculatedColumnFormula>L2/T2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{ACA15BF8-B0A7-481E-A7F2-D7E94E5D9CB0}" name="formula_no. of machines" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{ACA15BF8-B0A7-481E-A7F2-D7E94E5D9CB0}" name="formula_no. of machines" dataDxfId="22" totalsRowDxfId="21"/>
     <tableColumn id="22" xr3:uid="{0459E32F-2AB6-434A-9439-F5F08B7C6254}" name="no. of machines">
       <calculatedColumnFormula>V2/72</calculatedColumnFormula>
     </tableColumn>
@@ -1727,26 +1727,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T117"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" customWidth="1"/>
-    <col min="5" max="5" width="46.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.44140625" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" customWidth="1"/>
-    <col min="8" max="8" width="48.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1015625" customWidth="1"/>
+    <col min="2" max="2" width="13.3125" customWidth="1"/>
+    <col min="3" max="3" width="20.1015625" customWidth="1"/>
+    <col min="4" max="4" width="10.1015625" customWidth="1"/>
+    <col min="5" max="5" width="46.7890625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.41796875" customWidth="1"/>
+    <col min="7" max="7" width="20.7890625" customWidth="1"/>
+    <col min="8" max="8" width="48.41796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="40" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="31.5546875" customWidth="1"/>
-    <col min="14" max="14" width="26.21875" customWidth="1"/>
-    <col min="15" max="15" width="18.77734375" customWidth="1"/>
-    <col min="16" max="18" width="11.5546875" customWidth="1"/>
-    <col min="19" max="19" width="12.33203125" customWidth="1"/>
-    <col min="20" max="20" width="38.6640625" customWidth="1"/>
+    <col min="10" max="13" width="31.5234375" customWidth="1"/>
+    <col min="14" max="14" width="26.20703125" customWidth="1"/>
+    <col min="15" max="15" width="18.7890625" customWidth="1"/>
+    <col min="16" max="18" width="11.5234375" customWidth="1"/>
+    <col min="19" max="19" width="12.3125" customWidth="1"/>
+    <col min="20" max="20" width="38.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -2821,9 +2821,6 @@
       <c r="F22" t="s">
         <v>15</v>
       </c>
-      <c r="G22">
-        <v>52608</v>
-      </c>
       <c r="H22" t="s">
         <v>70</v>
       </c>
@@ -2852,7 +2849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -2902,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2952,7 +2949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -3002,7 +2999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -3052,7 +3049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -3099,7 +3096,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -3118,9 +3115,6 @@
       <c r="F28" t="s">
         <v>15</v>
       </c>
-      <c r="G28">
-        <v>52608</v>
-      </c>
       <c r="I28" t="s">
         <v>147</v>
       </c>
@@ -3149,7 +3143,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -3196,7 +3190,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -3243,7 +3237,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -3290,7 +3284,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -3337,7 +3331,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -3384,7 +3378,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -3431,7 +3425,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -3475,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -3522,7 +3516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -3569,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -3613,7 +3607,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -3657,7 +3651,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -3704,7 +3698,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -3751,7 +3745,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -3798,7 +3792,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -3845,7 +3839,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -3892,7 +3886,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -3939,7 +3933,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -3989,7 +3983,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -4039,7 +4033,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -4089,7 +4083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -4133,7 +4127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -4177,7 +4171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -4225,7 +4219,7 @@
       </c>
       <c r="T51" s="4"/>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
         <v>11</v>
       </c>
@@ -4273,7 +4267,7 @@
       </c>
       <c r="T52" s="4"/>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
         <v>11</v>
       </c>
@@ -4321,7 +4315,7 @@
       </c>
       <c r="T53" s="4"/>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
         <v>11</v>
       </c>
@@ -4369,7 +4363,7 @@
       </c>
       <c r="T54" s="1"/>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
         <v>11</v>
       </c>
@@ -4419,7 +4413,7 @@
       </c>
       <c r="T55" s="1"/>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
         <v>11</v>
       </c>
@@ -4469,7 +4463,7 @@
       </c>
       <c r="T56" s="1"/>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>11</v>
       </c>
@@ -4519,7 +4513,7 @@
       </c>
       <c r="T57" s="1"/>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
         <v>11</v>
       </c>
@@ -4571,7 +4565,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1" t="s">
         <v>11</v>
       </c>
@@ -4621,7 +4615,7 @@
       </c>
       <c r="T59" s="1"/>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
         <v>11</v>
       </c>
@@ -4671,7 +4665,7 @@
       </c>
       <c r="T60" s="1"/>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1" t="s">
         <v>11</v>
       </c>
@@ -4721,7 +4715,7 @@
       </c>
       <c r="T61" s="1"/>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1" t="s">
         <v>11</v>
       </c>
@@ -4773,7 +4767,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1" t="s">
         <v>11</v>
       </c>
@@ -4823,7 +4817,7 @@
       </c>
       <c r="T63" s="1"/>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1" t="s">
         <v>11</v>
       </c>
@@ -4873,7 +4867,7 @@
       </c>
       <c r="T64" s="1"/>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1" t="s">
         <v>11</v>
       </c>
@@ -4923,7 +4917,7 @@
       </c>
       <c r="T65" s="1"/>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1" t="s">
         <v>11</v>
       </c>
@@ -4975,7 +4969,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1" t="s">
         <v>11</v>
       </c>
@@ -5027,7 +5021,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1" t="s">
         <v>11</v>
       </c>
@@ -5079,7 +5073,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1" t="s">
         <v>11</v>
       </c>
@@ -5129,7 +5123,7 @@
       </c>
       <c r="T69" s="1"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1" t="s">
         <v>11</v>
       </c>
@@ -5179,7 +5173,7 @@
       </c>
       <c r="T70" s="1"/>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1" t="s">
         <v>11</v>
       </c>
@@ -5229,7 +5223,7 @@
       </c>
       <c r="T71" s="1"/>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1" t="s">
         <v>11</v>
       </c>
@@ -5281,7 +5275,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1" t="s">
         <v>11</v>
       </c>
@@ -5331,7 +5325,7 @@
       </c>
       <c r="T73" s="1"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="1" t="s">
         <v>11</v>
       </c>
@@ -5381,7 +5375,7 @@
       </c>
       <c r="T74" s="1"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1" t="s">
         <v>11</v>
       </c>
@@ -5433,7 +5427,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1" t="s">
         <v>11</v>
       </c>
@@ -5483,7 +5477,7 @@
       </c>
       <c r="T76" s="1"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="1" t="s">
         <v>11</v>
       </c>
@@ -5533,7 +5527,7 @@
       </c>
       <c r="T77" s="1"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1" t="s">
         <v>11</v>
       </c>
@@ -5585,7 +5579,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1" t="s">
         <v>11</v>
       </c>
@@ -5633,7 +5627,7 @@
       </c>
       <c r="T79" s="4"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1" t="s">
         <v>11</v>
       </c>
@@ -5681,7 +5675,7 @@
       </c>
       <c r="T80" s="4"/>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1" t="s">
         <v>11</v>
       </c>
@@ -5729,7 +5723,7 @@
       </c>
       <c r="T81" s="4"/>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1" t="s">
         <v>11</v>
       </c>
@@ -5777,7 +5771,7 @@
       </c>
       <c r="T82" s="4"/>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1" t="s">
         <v>11</v>
       </c>
@@ -5825,7 +5819,7 @@
       </c>
       <c r="T83" s="4"/>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1" t="s">
         <v>11</v>
       </c>
@@ -5873,7 +5867,7 @@
       </c>
       <c r="T84" s="4"/>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1" t="s">
         <v>11</v>
       </c>
@@ -5921,7 +5915,7 @@
       </c>
       <c r="T85" s="4"/>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1" t="s">
         <v>11</v>
       </c>
@@ -5969,7 +5963,7 @@
       </c>
       <c r="T86" s="4"/>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="1" t="s">
         <v>11</v>
       </c>
@@ -6017,7 +6011,7 @@
       </c>
       <c r="T87" s="4"/>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1" t="s">
         <v>11</v>
       </c>
@@ -6065,7 +6059,7 @@
       </c>
       <c r="T88" s="4"/>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1" t="s">
         <v>11</v>
       </c>
@@ -6113,7 +6107,7 @@
       </c>
       <c r="T89" s="4"/>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="1" t="s">
         <v>11</v>
       </c>
@@ -6161,7 +6155,7 @@
       </c>
       <c r="T90" s="4"/>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1" t="s">
         <v>11</v>
       </c>
@@ -6209,7 +6203,7 @@
       </c>
       <c r="T91" s="4"/>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1" t="s">
         <v>11</v>
       </c>
@@ -6257,7 +6251,7 @@
       </c>
       <c r="T92" s="4"/>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1" t="s">
         <v>11</v>
       </c>
@@ -6305,7 +6299,7 @@
       </c>
       <c r="T93" s="4"/>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1" t="s">
         <v>11</v>
       </c>
@@ -6353,7 +6347,7 @@
       </c>
       <c r="T94" s="4"/>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1" t="s">
         <v>11</v>
       </c>
@@ -6401,7 +6395,7 @@
       </c>
       <c r="T95" s="4"/>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1" t="s">
         <v>11</v>
       </c>
@@ -6449,7 +6443,7 @@
       </c>
       <c r="T96" s="4"/>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1" t="s">
         <v>11</v>
       </c>
@@ -6497,7 +6491,7 @@
       </c>
       <c r="T97" s="4"/>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1" t="s">
         <v>11</v>
       </c>
@@ -6545,7 +6539,7 @@
       </c>
       <c r="T98" s="4"/>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="1" t="s">
         <v>11</v>
       </c>
@@ -6593,7 +6587,7 @@
       </c>
       <c r="T99" s="4"/>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1" t="s">
         <v>11</v>
       </c>
@@ -6641,7 +6635,7 @@
       </c>
       <c r="T100" s="4"/>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1" t="s">
         <v>11</v>
       </c>
@@ -6689,7 +6683,7 @@
       </c>
       <c r="T101" s="4"/>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="1" t="s">
         <v>11</v>
       </c>
@@ -6737,7 +6731,7 @@
       </c>
       <c r="T102" s="1"/>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1" t="s">
         <v>11</v>
       </c>
@@ -6786,7 +6780,7 @@
       </c>
       <c r="T103" s="4"/>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1" t="s">
         <v>11</v>
       </c>
@@ -6835,7 +6829,7 @@
       </c>
       <c r="T104" s="4"/>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1" t="s">
         <v>11</v>
       </c>
@@ -6884,7 +6878,7 @@
       </c>
       <c r="T105" s="4"/>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1" t="s">
         <v>11</v>
       </c>
@@ -6933,7 +6927,7 @@
       </c>
       <c r="T106" s="4"/>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1" t="s">
         <v>11</v>
       </c>
@@ -6982,7 +6976,7 @@
       </c>
       <c r="T107" s="4"/>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1" t="s">
         <v>11</v>
       </c>
@@ -7031,7 +7025,7 @@
       </c>
       <c r="T108" s="4"/>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1" t="s">
         <v>11</v>
       </c>
@@ -7080,7 +7074,7 @@
       </c>
       <c r="T109" s="4"/>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1" t="s">
         <v>11</v>
       </c>
@@ -7129,7 +7123,7 @@
       </c>
       <c r="T110" s="4"/>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="1" t="s">
         <v>11</v>
       </c>
@@ -7178,7 +7172,7 @@
       </c>
       <c r="T111" s="4"/>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1" t="s">
         <v>11</v>
       </c>
@@ -7225,7 +7219,7 @@
       </c>
       <c r="T112" s="4"/>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1" t="s">
         <v>11</v>
       </c>
@@ -7272,7 +7266,7 @@
       </c>
       <c r="T113" s="4"/>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="1" t="s">
         <v>11</v>
       </c>
@@ -7319,7 +7313,7 @@
       </c>
       <c r="T114" s="4"/>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="1" t="s">
         <v>11</v>
       </c>
@@ -7368,7 +7362,7 @@
       </c>
       <c r="T115" s="4"/>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="1" t="s">
         <v>11</v>
       </c>
@@ -7417,7 +7411,7 @@
       </c>
       <c r="T116" s="4"/>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1" t="s">
         <v>11</v>
       </c>
@@ -7478,35 +7472,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6343EE0-D320-4977-9825-4200D3368BED}">
   <dimension ref="A1:X37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="17.41796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3125" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="8.3125" customWidth="1"/>
+    <col min="5" max="5" width="19.41796875" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.3125" customWidth="1"/>
     <col min="8" max="8" width="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="46.6640625" customWidth="1"/>
-    <col min="10" max="10" width="43.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.33203125" customWidth="1"/>
-    <col min="12" max="12" width="34.6640625" customWidth="1"/>
-    <col min="13" max="13" width="23.21875" customWidth="1"/>
-    <col min="14" max="14" width="34.88671875" customWidth="1"/>
-    <col min="15" max="15" width="26.77734375" customWidth="1"/>
-    <col min="16" max="16" width="39.33203125" customWidth="1"/>
-    <col min="17" max="17" width="13.77734375" customWidth="1"/>
-    <col min="18" max="18" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="45.109375" customWidth="1"/>
-    <col min="20" max="20" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="49.88671875" customWidth="1"/>
-    <col min="22" max="22" width="25.109375" customWidth="1"/>
+    <col min="9" max="9" width="46.68359375" customWidth="1"/>
+    <col min="10" max="10" width="43.3125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.3125" customWidth="1"/>
+    <col min="12" max="12" width="34.68359375" customWidth="1"/>
+    <col min="13" max="13" width="23.20703125" customWidth="1"/>
+    <col min="14" max="14" width="34.89453125" customWidth="1"/>
+    <col min="15" max="15" width="26.7890625" customWidth="1"/>
+    <col min="16" max="16" width="39.3125" customWidth="1"/>
+    <col min="17" max="17" width="13.7890625" customWidth="1"/>
+    <col min="18" max="18" width="33.41796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="45.1015625" customWidth="1"/>
+    <col min="20" max="20" width="40.41796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="49.89453125" customWidth="1"/>
+    <col min="22" max="22" width="25.1015625" customWidth="1"/>
     <col min="23" max="23" width="17" customWidth="1"/>
-    <col min="24" max="24" width="15.5546875" customWidth="1"/>
+    <col min="24" max="24" width="15.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>196</v>
       </c>
@@ -7580,7 +7574,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>218</v>
       </c>
@@ -7661,7 +7655,7 @@
         <v>2.5516553150693633</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>218</v>
       </c>
@@ -7718,7 +7712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>222</v>
       </c>
@@ -7783,7 +7777,7 @@
         <v>0.42808153681559535</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>224</v>
       </c>
@@ -7848,7 +7842,7 @@
         <v>2.7111830664987711</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>225</v>
       </c>
@@ -7913,7 +7907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>226</v>
       </c>
@@ -7978,7 +7972,7 @@
         <v>0.18992832745236415</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>227</v>
       </c>
@@ -8043,7 +8037,7 @@
         <v>0.40861677010253639</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>228</v>
       </c>
@@ -8108,7 +8102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>228</v>
       </c>
@@ -8173,7 +8167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>230</v>
       </c>
@@ -8238,7 +8232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>231</v>
       </c>
@@ -8303,7 +8297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>232</v>
       </c>
@@ -8368,7 +8362,7 @@
         <v>0.70165756054775441</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>233</v>
       </c>
@@ -8433,7 +8427,7 @@
         <v>1.2948798803565318</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>234</v>
       </c>
@@ -8498,7 +8492,7 @@
         <v>0.77291166383862875</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>235</v>
       </c>
@@ -8563,7 +8557,7 @@
         <v>1.1040147594260059</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>236</v>
       </c>
@@ -8628,7 +8622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>237</v>
       </c>
@@ -8693,7 +8687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>238</v>
       </c>
@@ -8761,7 +8755,7 @@
         <v>0.118974377457405</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -8814,7 +8808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -8859,7 +8853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -8904,7 +8898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -8949,7 +8943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -8994,7 +8988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -9039,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -9084,7 +9078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -9129,7 +9123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -9174,7 +9168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -9219,7 +9213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -9261,7 +9255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -9303,7 +9297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -9345,7 +9339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -9390,7 +9384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -9435,7 +9429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>11</v>
       </c>
